--- a/30_table/01_테스트버전/Table_List_Region.xlsx
+++ b/30_table/01_테스트버전/Table_List_Region.xlsx
@@ -13,14 +13,14 @@
     <sheet name="Type" sheetId="9" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Data!$E$1:$E$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Data!$E$1:$E$5</definedName>
   </definedNames>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -166,14 +166,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>죽은 자의 동굴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>광산 마을</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>region_01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -182,12 +174,6 @@
   </si>
   <si>
     <t>region_03</t>
-  </si>
-  <si>
-    <t>region_04</t>
-  </si>
-  <si>
-    <t>region_05</t>
   </si>
   <si>
     <t>Icon</t>
@@ -201,6 +187,14 @@
   </si>
   <si>
     <t>icon_map_0012</t>
+  </si>
+  <si>
+    <t>개발실</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>region_99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3570,7 +3564,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="17"/>
@@ -3594,7 +3588,7 @@
         <v>18</v>
       </c>
       <c r="E1" s="29" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="35" customFormat="1" x14ac:dyDescent="0.3">
@@ -3605,14 +3599,14 @@
         <v>31</v>
       </c>
       <c r="C2" s="34" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D2" s="34" t="str">
         <f>"STR_"&amp;UPPER(C2)</f>
         <v>STR_REGION_01</v>
       </c>
       <c r="E2" s="34" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="35" customFormat="1" x14ac:dyDescent="0.3">
@@ -3623,14 +3617,14 @@
         <v>32</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D3" s="34" t="str">
-        <f t="shared" ref="D3:D6" si="0">"STR_"&amp;UPPER(C3)</f>
+        <f t="shared" ref="D3:D5" si="0">"STR_"&amp;UPPER(C3)</f>
         <v>STR_REGION_02</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="35" customFormat="1" x14ac:dyDescent="0.3">
@@ -3641,50 +3635,32 @@
         <v>33</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D4" s="34" t="str">
         <f t="shared" si="0"/>
         <v>STR_REGION_03</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="31">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D5" s="34" t="str">
         <f t="shared" si="0"/>
-        <v>STR_REGION_04</v>
+        <v>STR_REGION_99</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="35" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="31">
-        <v>5</v>
-      </c>
-      <c r="B6" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="34" t="s">
         <v>42</v>
-      </c>
-      <c r="D6" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v>STR_REGION_05</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/30_table/01_테스트버전/Table_List_Region.xlsx
+++ b/30_table/01_테스트버전/Table_List_Region.xlsx
@@ -13,14 +13,14 @@
     <sheet name="Type" sheetId="9" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Data!$E$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Data!$E$1:$E$6</definedName>
   </definedNames>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="48">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -194,6 +194,17 @@
   </si>
   <si>
     <t>region_99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>region_04</t>
+  </si>
+  <si>
+    <t>죽은 자의 동굴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_map_0022</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3564,7 +3575,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="17"/>
@@ -3620,7 +3631,7 @@
         <v>37</v>
       </c>
       <c r="D3" s="34" t="str">
-        <f t="shared" ref="D3:D5" si="0">"STR_"&amp;UPPER(C3)</f>
+        <f t="shared" ref="D3:D6" si="0">"STR_"&amp;UPPER(C3)</f>
         <v>STR_REGION_02</v>
       </c>
       <c r="E3" s="34" t="s">
@@ -3647,19 +3658,37 @@
     </row>
     <row r="5" spans="1:5" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="34" t="str">
+        <f t="shared" ref="D5" si="1">"STR_"&amp;UPPER(C5)</f>
+        <v>STR_REGION_04</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="31">
         <v>99</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B6" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C6" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="34" t="str">
+      <c r="D6" s="34" t="str">
         <f t="shared" si="0"/>
         <v>STR_REGION_99</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="E6" s="34" t="s">
         <v>42</v>
       </c>
     </row>
